--- a/data/mapas/Mapa_de_Carrera_Economia.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Economia.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B52, "SI")</f>
+        <f>COUNTIF(B6:B42, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C52, "SI")</f>
+        <f>COUNTIF(C6:C42, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F52, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F42, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Principios de Economía y Microeconomía I</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B52, "SI")/41</f>
+        <f>COUNTIF(B6:B42, "SI")/33</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Matemática para Economistas I (Álgebra y Cálculo)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C52, "SI")/41</f>
+        <f>COUNTIF(C6:C42, "SI")/33</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Disciplina</t>
+          <t>Historia del Pensamiento Económico I</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente I</t>
+          <t>Contabilidad General y Social</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -831,10 +831,37 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Pedagogía</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(B10="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="SI", "APROBADO", IF(B10="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(C10="SI", "🟢 Aprobada", IF(B10="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -921,37 +948,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Sujetos de la Educación</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente II</t>
+          <t>Macroeconomía I</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -999,10 +999,37 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Microeconomía II</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E15" s="10">
+        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Matemática para Economistas II</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Estadística Económica</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Historia Económica Argentina y Mundial</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1115,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1130,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1146,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Psicología Educacional</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Sujetos de la Educación</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1190,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1205,7 +1259,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E22" s="10">
@@ -1221,44 +1275,17 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Investigación Educativa</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E23" s="10">
-        <f>IF(B23="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>IF(C23="SI", "APROBADO", IF(B23="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G23" s="11">
-        <f>IF(C23="SI", "🟢 Aprobada", IF(B23="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente IV</t>
+          <t>Macroeconomía II (Dinero, Crédito y Bancos)</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1273,7 +1300,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1289,17 +1316,44 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Economía Internacional y Comercio Exterior</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Finanzas Públicas y Política Fiscal</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Didáctica de la Economía I</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1401,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1416,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1432,51 +1486,51 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Especialización Superior II</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E31" s="10">
-        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G31" s="11">
-        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la Práctica Docente I</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Desarrollo Económico y Estructura Productiva Argentina</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1491,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1510,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior II</t>
+          <t>Economía Política y Distribución del Ingreso</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1544,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Formulación y Evaluación de Proyectos</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1559,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1575,17 +1629,44 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>📌 GENERAL / OPTATIVAS</t>
-        </is>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica de la Economía II</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Didáctica ESP. Y CONST. Práctica DOCENTE I</t>
+          <t>Educación Sexual Integral (ESI)</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1600,7 +1681,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1619,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Dinero, Credito y Bancos</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1634,7 +1715,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1653,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Econometria</t>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1668,7 +1749,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E38" s="10">
@@ -1684,44 +1765,17 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Estadistica</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E39" s="10">
-        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
-        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G39" s="11">
-        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Filosofía</t>
+          <t>Seminario de Economía Social y Cooperativismo</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1736,7 +1790,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1755,7 +1809,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Finanzas Publicas</t>
+          <t>Seminario de Integración Económica Regional</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1770,7 +1824,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1789,7 +1843,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Historia del Pensamiento Economico</t>
+          <t>Taller de Investigación Económica</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1804,7 +1858,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1820,368 +1874,26 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>INTRODUCCION A LA Economía</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E43" s="10">
-        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G43" s="11">
-        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>Introduccion a la Eonomia</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E44" s="10">
-        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F44" s="10">
-        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G44" s="11">
-        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Lectura Escritura y Oralidad II</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E45" s="10">
-        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Macroeconomia</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>METODOLOGIA DE LA Investigación</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E47" s="10">
-        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Taller de Aplicativos Informaticos</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E48" s="10">
-        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>TALLER DE Informática</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E49" s="10">
-        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G49" s="11">
-        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo de Campo I</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E50" s="10">
-        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G50" s="11">
-        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Derecho Público</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E51" s="10">
-        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G51" s="11">
-        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Microeconomía</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E52" s="10">
-        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="I14:J14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B11 B12 B13 B14 B16 B17 B18 B19 B21 B22 B23 B24 B26 B27 B28 B29 B31 B32 B33 B34 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 C6 C7 C8 C9 C11 C12 C13 C14 C16 C17 C18 C19 C21 C22 C23 C24 C26 C27 C28 C29 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B22 B24 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B38 B40 B41 B42 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C22 C24 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C38 C40 C41 C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Economia.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Economia.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B42, "SI")</f>
+        <f>COUNTIF(B6:B49, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C42, "SI")</f>
+        <f>COUNTIF(C6:C49, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F42, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F49, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Principios de Economía y Microeconomía I</t>
+          <t>Sistenas de información contable</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B42, "SI")/33</f>
+        <f>COUNTIF(B6:B49, "SI")/40</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Matemática para Economistas I (Álgebra y Cálculo)</t>
+          <t>Analisis matemático</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C42, "SI")/33</f>
+        <f>COUNTIF(C6:C49, "SI")/40</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Historia del Pensamiento Económico I</t>
+          <t>Derecho publico</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Contabilidad General y Social</t>
+          <t>Introduccion a la economía</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Historia economica general y Argentina</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,10 +948,37 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Psicología Educacional</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +989,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Macroeconomía I</t>
+          <t>Sujetos de la enseñanza</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -977,7 +1004,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Microeconomía II</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1037,44 +1064,17 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Matemática para Economistas II</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E16" s="10">
-        <f>IF(B16="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>IF(C16="SI", "APROBADO", IF(B16="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>IF(C16="SI", "🟢 Aprobada", IF(B16="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Estadística Económica</t>
+          <t>Principios de administración</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Historia Económica Argentina y Mundial</t>
+          <t>Estadistica</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Derecho civil y societario</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Didactica general</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Geografia economica</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1275,17 +1275,44 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Lectura, Escritura y Oralidad II (LEO 2)</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E23" s="10">
+        <f>IF(B23="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>IF(C23="SI", "APROBADO", IF(B23="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="11">
+        <f>IF(C23="SI", "🟢 Aprobada", IF(B23="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Macroeconomía II (Dinero, Crédito y Bancos)</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1300,7 +1327,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1316,44 +1343,17 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Economía Internacional y Comercio Exterior</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E25" s="10">
-        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
-        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G25" s="11">
-        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Finanzas Públicas y Política Fiscal</t>
+          <t>Microeconomía</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Economía I</t>
+          <t>Finanzas publicas</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Didactica especifica y construcción de la practica docente 1</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Historia del pensamiento economico</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente I</t>
+          <t>Historia de la educación Argentina</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1520,17 +1520,44 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>DDHH, sociedad y estado</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E31" s="10">
+        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Desarrollo Económico y Estructura Productiva Argentina</t>
+          <t>Sem/taller opt. Economias comparadas</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Economía Política y Distribución del Ingreso</t>
+          <t>Sem/taller opt. Politica economia</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1595,44 +1622,17 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Formulación y Evaluación de Proyectos</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E34" s="10">
-        <f>IF(B34="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F34" s="10">
-        <f>IF(C34="SI", "APROBADO", IF(B34="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G34" s="11">
-        <f>IF(C34="SI", "🟢 Aprobada", IF(B34="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Economía II</t>
+          <t>Macroeconomia</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Crecimiento y desarrollo economico</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Dinero, credito y bancos</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
+          <t>Aplicativos informaticos</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1765,17 +1765,44 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Metodología de la investigación</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E39" s="10">
+        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
+        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Economía Social y Cooperativismo</t>
+          <t>Taller de nuevas tecnologias</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1817,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1809,7 +1836,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Integración Económica Regional</t>
+          <t>Sistema y politica educativa</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1851,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1843,7 +1870,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Económica</t>
+          <t>Didactica de la educación superior</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1858,7 +1885,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1874,26 +1901,237 @@
         <v/>
       </c>
     </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Didactica de la educación a distancia</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Taller de idioma extranjero ingles</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Taller de informatica</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Esi</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la practica docente 2</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Econometria</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B22 B24 B25 B26 B27 B28 B29 B30 B32 B33 B34 B35 B36 B37 B38 B40 B41 B42 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C22 C24 C25 C26 C27 C28 C29 C30 C32 C33 C34 C35 C36 C37 C38 C40 C41 C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B17 B18 B19 B20 B21 B22 B23 B24 B26 B27 B28 B29 B30 B31 B32 B33 B35 B36 B37 B38 B39 B40 B41 B42 B43 B45 B46 B47 B48 B49 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C17 C18 C19 C20 C21 C22 C23 C24 C26 C27 C28 C29 C30 C31 C32 C33 C35 C36 C37 C38 C39 C40 C41 C42 C43 C45 C46 C47 C48 C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
